--- a/Excels/SoliderUnit.xlsx
+++ b/Excels/SoliderUnit.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="53">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -49,10 +49,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>刀盾近战</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>skill</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -109,7 +105,126 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>showName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>显示名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三国短锤兵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三国弓兵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三国炮兵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>炮兵</t>
+  </si>
+  <si>
+    <t>三国长锤兵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>长锤兵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>短锤兵</t>
+  </si>
+  <si>
+    <t>弓兵</t>
+  </si>
+  <si>
+    <t>三国刀盾兵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刀盾兵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三国弩兵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弩兵</t>
+  </si>
+  <si>
+    <t>三国枪兵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>枪兵</t>
+  </si>
+  <si>
     <t>Soldier/Soldier1_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soldier/Soldier2_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soldier/Soldier3_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soldier/Soldier4_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soldier/Soldier6_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soldier/Soldier7_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soldier/Soldier8_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弩车</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soldier/Soldier10_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>骑兵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soldier/Soldier11_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>投石车</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soldier/Soldier12_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冲车</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soldier/Soldier15_1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -427,7 +542,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -435,17 +550,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
-    <col min="2" max="2" width="18.08203125" customWidth="1"/>
-    <col min="3" max="3" width="19.4140625" customWidth="1"/>
-    <col min="5" max="7" width="81.83203125" customWidth="1"/>
-    <col min="8" max="8" width="57.25" customWidth="1"/>
+    <col min="2" max="3" width="18.08203125" customWidth="1"/>
+    <col min="4" max="4" width="19.4140625" customWidth="1"/>
+    <col min="6" max="8" width="81.83203125" customWidth="1"/>
+    <col min="9" max="9" width="57.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -453,25 +568,28 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" t="s">
         <v>13</v>
       </c>
-      <c r="F1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -479,25 +597,28 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E2" t="s">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -505,48 +626,344 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13">
         <v>10</v>
       </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4" t="s">
-        <v>22</v>
+      <c r="B13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/Excels/SoliderUnit.xlsx
+++ b/Excels/SoliderUnit.xlsx
@@ -542,7 +542,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>

--- a/Excels/SoliderUnit.xlsx
+++ b/Excels/SoliderUnit.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="90">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -105,10 +105,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>showName</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -117,90 +113,151 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>三国短锤兵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>三国弓兵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>三国炮兵</t>
+    <t>长锤兵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刀盾兵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soldier/Soldier1_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soldier/Soldier2_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soldier/Soldier3_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soldier/Soldier4_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soldier/Soldier6_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soldier/Soldier7_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soldier/Soldier8_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弩车</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soldier/Soldier10_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>骑兵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soldier/Soldier11_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>投石车</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soldier/Soldier12_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冲车</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soldier/Soldier15_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弓兵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>短锤兵</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>炮兵</t>
-  </si>
-  <si>
-    <t>三国长锤兵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>长锤兵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>短锤兵</t>
-  </si>
-  <si>
-    <t>弓兵</t>
-  </si>
-  <si>
-    <t>三国刀盾兵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>刀盾兵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>三国弩兵</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>弩兵</t>
-  </si>
-  <si>
-    <t>三国枪兵</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>枪兵</t>
-  </si>
-  <si>
-    <t>Soldier/Soldier1_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Soldier/Soldier2_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Soldier/Soldier3_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Soldier/Soldier4_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Soldier/Soldier6_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Soldier/Soldier7_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Soldier/Soldier8_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>弩车</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Soldier/Soldier10_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>des</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刀盾兵(三)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弓兵(三)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>短锤兵(三)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>炮兵(三)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>长锤兵(三)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弩兵(三)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>枪兵(三)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弩车(三)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>骑兵(三)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>投石车(三)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冲车(三)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刀盾兵(秦)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弓兵(秦)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>枪兵(秦)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -208,23 +265,119 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Soldier/Soldier11_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>投石车</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Soldier/Soldier12_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>冲车</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Soldier/Soldier15_1</t>
+    <t>骑兵(秦)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弩车(秦)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>投石车(秦)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冲车(秦)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吕布</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘备</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>关羽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>张飞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赵云</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吕布(三)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘备(三)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>关羽(三)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>张飞(三)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赵云(三)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>项羽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘邦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>韩信</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>樊哙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>项庄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>项羽(秦)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘邦(秦)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>韩信(秦)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>樊哙(秦)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>项庄(秦)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soldier/Hero13_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soldier/Hero12_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soldier/Hero22_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soldier/Hero10_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soldier/Hero11_1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -542,7 +695,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -550,7 +703,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
@@ -568,7 +721,7 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="D1" t="s">
         <v>7</v>
@@ -597,7 +750,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
         <v>8</v>
@@ -626,7 +779,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
         <v>9</v>
@@ -649,13 +802,13 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -673,18 +826,18 @@
         <v>1</v>
       </c>
       <c r="I4" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -702,18 +855,18 @@
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6">
-        <v>3</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -731,18 +884,18 @@
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7">
-        <v>4</v>
+        <v>104</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -760,47 +913,47 @@
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8">
-        <v>5</v>
+        <v>105</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8" t="s">
         <v>29</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9">
-        <v>6</v>
+        <v>106</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -818,18 +971,18 @@
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10">
-        <v>7</v>
+        <v>107</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -847,18 +1000,18 @@
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11">
-        <v>8</v>
+        <v>108</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D11">
         <v>2</v>
@@ -876,18 +1029,18 @@
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -905,18 +1058,18 @@
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -934,18 +1087,18 @@
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14">
-        <v>11</v>
+        <v>111</v>
       </c>
       <c r="B14" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -963,7 +1116,485 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>52</v>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15">
+        <v>201</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16">
+        <v>202</v>
+      </c>
+      <c r="B16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16">
+        <v>2</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17">
+        <v>203</v>
+      </c>
+      <c r="B17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18">
+        <v>204</v>
+      </c>
+      <c r="B18" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19">
+        <v>205</v>
+      </c>
+      <c r="B19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" t="s">
+        <v>62</v>
+      </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20">
+        <v>206</v>
+      </c>
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20">
+        <v>2</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21">
+        <v>207</v>
+      </c>
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22">
+        <v>1001</v>
+      </c>
+      <c r="B22" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" t="s">
+        <v>70</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23">
+        <v>1002</v>
+      </c>
+      <c r="B23" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" t="s">
+        <v>71</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24">
+        <v>1003</v>
+      </c>
+      <c r="B24" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" t="s">
+        <v>72</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25">
+        <v>1004</v>
+      </c>
+      <c r="B25" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26">
+        <v>1005</v>
+      </c>
+      <c r="B26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C26" t="s">
+        <v>74</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27">
+        <v>2001</v>
+      </c>
+      <c r="B27" t="s">
+        <v>75</v>
+      </c>
+      <c r="C27" t="s">
+        <v>80</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28">
+        <v>2002</v>
+      </c>
+      <c r="B28" t="s">
+        <v>76</v>
+      </c>
+      <c r="C28" t="s">
+        <v>81</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29">
+        <v>2003</v>
+      </c>
+      <c r="B29" t="s">
+        <v>77</v>
+      </c>
+      <c r="C29" t="s">
+        <v>82</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30">
+        <v>2004</v>
+      </c>
+      <c r="B30" t="s">
+        <v>78</v>
+      </c>
+      <c r="C30" t="s">
+        <v>83</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31">
+        <v>2005</v>
+      </c>
+      <c r="B31" t="s">
+        <v>79</v>
+      </c>
+      <c r="C31" t="s">
+        <v>84</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Excels/SoliderUnit.xlsx
+++ b/Excels/SoliderUnit.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="98">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -378,6 +378,38 @@
   </si>
   <si>
     <t>Soldier/Hero11_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soldier/Hero33_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soldier/Hero26_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soldier/Hero43_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soldier/Hero38_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soldier/Hero34_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unitType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0无 1刀2枪3骑  11 攻城器 101英雄     （兵种属性和克制 1 克 2 ， 2 克 3， 3克1 ， 0被所有克)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -695,7 +727,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -703,17 +735,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
     <col min="2" max="3" width="18.08203125" customWidth="1"/>
     <col min="4" max="4" width="19.4140625" customWidth="1"/>
-    <col min="6" max="8" width="81.83203125" customWidth="1"/>
-    <col min="9" max="9" width="57.25" customWidth="1"/>
+    <col min="6" max="9" width="81.83203125" customWidth="1"/>
+    <col min="10" max="10" width="57.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -739,10 +771,13 @@
         <v>19</v>
       </c>
       <c r="I1" t="s">
+        <v>95</v>
+      </c>
+      <c r="J1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -768,10 +803,13 @@
         <v>16</v>
       </c>
       <c r="I2" t="s">
+        <v>96</v>
+      </c>
+      <c r="J2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -797,10 +835,13 @@
         <v>20</v>
       </c>
       <c r="I3" t="s">
+        <v>97</v>
+      </c>
+      <c r="J3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:10">
       <c r="A4">
         <v>101</v>
       </c>
@@ -825,11 +866,14 @@
       <c r="H4">
         <v>1</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:10">
       <c r="A5">
         <v>102</v>
       </c>
@@ -854,11 +898,14 @@
       <c r="H5">
         <v>1</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:10">
       <c r="A6">
         <v>103</v>
       </c>
@@ -883,11 +930,14 @@
       <c r="H6">
         <v>1</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:10">
       <c r="A7">
         <v>104</v>
       </c>
@@ -912,11 +962,14 @@
       <c r="H7">
         <v>1</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:10">
       <c r="A8">
         <v>105</v>
       </c>
@@ -941,11 +994,14 @@
       <c r="H8">
         <v>1</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I8">
+        <v>2</v>
+      </c>
+      <c r="J8" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:10">
       <c r="A9">
         <v>106</v>
       </c>
@@ -970,11 +1026,14 @@
       <c r="H9">
         <v>1</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:10">
       <c r="A10">
         <v>107</v>
       </c>
@@ -999,11 +1058,14 @@
       <c r="H10">
         <v>1</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10">
+        <v>2</v>
+      </c>
+      <c r="J10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:10">
       <c r="A11">
         <v>108</v>
       </c>
@@ -1028,11 +1090,14 @@
       <c r="H11">
         <v>1</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I11">
+        <v>11</v>
+      </c>
+      <c r="J11" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:10">
       <c r="A12">
         <v>109</v>
       </c>
@@ -1057,11 +1122,14 @@
       <c r="H12">
         <v>1</v>
       </c>
-      <c r="I12" t="s">
+      <c r="I12">
+        <v>3</v>
+      </c>
+      <c r="J12" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:10">
       <c r="A13">
         <v>110</v>
       </c>
@@ -1086,11 +1154,14 @@
       <c r="H13">
         <v>1</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I13">
+        <v>11</v>
+      </c>
+      <c r="J13" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:10">
       <c r="A14">
         <v>111</v>
       </c>
@@ -1115,11 +1186,14 @@
       <c r="H14">
         <v>1</v>
       </c>
-      <c r="I14" t="s">
+      <c r="I14">
+        <v>11</v>
+      </c>
+      <c r="J14" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:10">
       <c r="A15">
         <v>201</v>
       </c>
@@ -1144,11 +1218,14 @@
       <c r="H15">
         <v>1</v>
       </c>
-      <c r="I15" t="s">
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:10">
       <c r="A16">
         <v>202</v>
       </c>
@@ -1173,11 +1250,14 @@
       <c r="H16">
         <v>1</v>
       </c>
-      <c r="I16" t="s">
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:10">
       <c r="A17">
         <v>203</v>
       </c>
@@ -1202,11 +1282,14 @@
       <c r="H17">
         <v>1</v>
       </c>
-      <c r="I17" t="s">
+      <c r="I17">
+        <v>2</v>
+      </c>
+      <c r="J17" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:10">
       <c r="A18">
         <v>204</v>
       </c>
@@ -1231,11 +1314,14 @@
       <c r="H18">
         <v>1</v>
       </c>
-      <c r="I18" t="s">
+      <c r="I18">
+        <v>3</v>
+      </c>
+      <c r="J18" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:10">
       <c r="A19">
         <v>205</v>
       </c>
@@ -1260,11 +1346,14 @@
       <c r="H19">
         <v>1</v>
       </c>
-      <c r="I19" t="s">
+      <c r="I19">
+        <v>11</v>
+      </c>
+      <c r="J19" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:10">
       <c r="A20">
         <v>206</v>
       </c>
@@ -1289,11 +1378,14 @@
       <c r="H20">
         <v>1</v>
       </c>
-      <c r="I20" t="s">
+      <c r="I20">
+        <v>11</v>
+      </c>
+      <c r="J20" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:10">
       <c r="A21">
         <v>207</v>
       </c>
@@ -1318,11 +1410,14 @@
       <c r="H21">
         <v>1</v>
       </c>
-      <c r="I21" t="s">
+      <c r="I21">
+        <v>11</v>
+      </c>
+      <c r="J21" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:10">
       <c r="A22">
         <v>1001</v>
       </c>
@@ -1347,11 +1442,14 @@
       <c r="H22">
         <v>1</v>
       </c>
-      <c r="I22" t="s">
+      <c r="I22">
+        <v>101</v>
+      </c>
+      <c r="J22" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:10">
       <c r="A23">
         <v>1002</v>
       </c>
@@ -1376,11 +1474,14 @@
       <c r="H23">
         <v>1</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23">
+        <v>101</v>
+      </c>
+      <c r="J23" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:10">
       <c r="A24">
         <v>1003</v>
       </c>
@@ -1405,11 +1506,14 @@
       <c r="H24">
         <v>1</v>
       </c>
-      <c r="I24" t="s">
+      <c r="I24">
+        <v>101</v>
+      </c>
+      <c r="J24" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:10">
       <c r="A25">
         <v>1004</v>
       </c>
@@ -1434,11 +1538,14 @@
       <c r="H25">
         <v>1</v>
       </c>
-      <c r="I25" t="s">
+      <c r="I25">
+        <v>101</v>
+      </c>
+      <c r="J25" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:10">
       <c r="A26">
         <v>1005</v>
       </c>
@@ -1463,11 +1570,14 @@
       <c r="H26">
         <v>1</v>
       </c>
-      <c r="I26" t="s">
+      <c r="I26">
+        <v>101</v>
+      </c>
+      <c r="J26" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:10">
       <c r="A27">
         <v>2001</v>
       </c>
@@ -1492,8 +1602,14 @@
       <c r="H27">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:9">
+      <c r="I27">
+        <v>101</v>
+      </c>
+      <c r="J27" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28">
         <v>2002</v>
       </c>
@@ -1518,8 +1634,14 @@
       <c r="H28">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:9">
+      <c r="I28">
+        <v>101</v>
+      </c>
+      <c r="J28" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29">
         <v>2003</v>
       </c>
@@ -1544,8 +1666,14 @@
       <c r="H29">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:9">
+      <c r="I29">
+        <v>101</v>
+      </c>
+      <c r="J29" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30">
         <v>2004</v>
       </c>
@@ -1570,8 +1698,14 @@
       <c r="H30">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:9">
+      <c r="I30">
+        <v>101</v>
+      </c>
+      <c r="J30" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31">
         <v>2005</v>
       </c>
@@ -1595,6 +1729,12 @@
       </c>
       <c r="H31">
         <v>1</v>
+      </c>
+      <c r="I31">
+        <v>101</v>
+      </c>
+      <c r="J31" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/Excels/SoliderUnit.xlsx
+++ b/Excels/SoliderUnit.xlsx
@@ -1,447 +1,702 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="4180" yWindow="4180" windowWidth="32770" windowHeight="16910"/>
+    <workbookView windowWidth="28800" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="SoliderCfg" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
-  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="101">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>des</t>
+  </si>
+  <si>
+    <t>skill</t>
+  </si>
+  <si>
+    <t>hp</t>
+  </si>
+  <si>
+    <t>atk</t>
+  </si>
+  <si>
+    <t>moveSpeed</t>
+  </si>
+  <si>
+    <t>radius</t>
+  </si>
+  <si>
+    <t>unitType</t>
+  </si>
+  <si>
+    <t>prefab</t>
+  </si>
   <si>
     <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>int[]</t>
+  </si>
+  <si>
+    <t>float</t>
   </si>
   <si>
     <t>#备注行</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>名字</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>显示名称</t>
+  </si>
+  <si>
+    <t>技能Id</t>
+  </si>
+  <si>
+    <t>血量</t>
   </si>
   <si>
     <t>伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>skill</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int[]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能Id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>血量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>atk</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>prefab</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>移动速度</t>
+  </si>
+  <si>
+    <t>身体范围</t>
+  </si>
+  <si>
+    <t>0无 1刀2枪3骑  11 攻城器 101英雄     （兵种属性和克制 1 克 2 ， 2 克 3， 3克1 ， 0被所有克)</t>
   </si>
   <si>
     <t>预制体名字</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>float</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>moveSpeed</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>移动速度</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>radius</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>身体范围</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>显示名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刀盾兵</t>
+  </si>
+  <si>
+    <t>刀盾兵(三)</t>
+  </si>
+  <si>
+    <t>Soldier/Soldier1_1</t>
+  </si>
+  <si>
+    <t>弓兵</t>
+  </si>
+  <si>
+    <t>弓兵(三)</t>
+  </si>
+  <si>
+    <t>Soldier/Soldier2_1</t>
+  </si>
+  <si>
+    <t>短锤兵</t>
+  </si>
+  <si>
+    <t>短锤兵(三)</t>
+  </si>
+  <si>
+    <t>Soldier/Soldier3_1</t>
+  </si>
+  <si>
+    <t>炮兵</t>
+  </si>
+  <si>
+    <t>炮兵(三)</t>
+  </si>
+  <si>
+    <t>Soldier/Soldier4_1</t>
   </si>
   <si>
     <t>长锤兵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>刀盾兵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Soldier/Soldier1_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Soldier/Soldier2_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Soldier/Soldier3_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Soldier/Soldier4_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>长锤兵(三)</t>
   </si>
   <si>
     <t>Soldier/Soldier6_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弩兵</t>
+  </si>
+  <si>
+    <t>弩兵(三)</t>
   </si>
   <si>
     <t>Soldier/Soldier7_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>枪兵</t>
+  </si>
+  <si>
+    <t>枪兵(三)</t>
   </si>
   <si>
     <t>Soldier/Soldier8_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>弩车</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弩车(三)</t>
   </si>
   <si>
     <t>Soldier/Soldier10_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>骑兵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>骑兵(三)</t>
   </si>
   <si>
     <t>Soldier/Soldier11_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>投石车</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>投石车(三)</t>
   </si>
   <si>
     <t>Soldier/Soldier12_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>冲车</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冲车(三)</t>
   </si>
   <si>
     <t>Soldier/Soldier15_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>弓兵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>短锤兵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>炮兵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>弩兵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>枪兵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>des</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>刀盾兵(三)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>弓兵(三)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>短锤兵(三)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>炮兵(三)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>长锤兵(三)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>弩兵(三)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>枪兵(三)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>弩车(三)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>骑兵(三)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>投石车(三)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>冲车(三)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>刀盾兵(秦)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soldier/Soldier1_2_qin</t>
   </si>
   <si>
     <t>弓兵(秦)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soldier/Soldier2_2_qin</t>
   </si>
   <si>
     <t>枪兵(秦)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>骑兵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soldier/Soldier8_2_qin</t>
   </si>
   <si>
     <t>骑兵(秦)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soldier/Soldier11_2_qin</t>
   </si>
   <si>
     <t>弩车(秦)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soldier/Soldier10_2_qin</t>
   </si>
   <si>
     <t>投石车(秦)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soldier/Soldier12_2_qin</t>
   </si>
   <si>
     <t>冲车(秦)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soldier/Soldier15_2_qin</t>
   </si>
   <si>
     <t>吕布</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吕布(三)</t>
+  </si>
+  <si>
+    <t>Soldier/Hero22_1</t>
   </si>
   <si>
     <t>刘备</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘备(三)</t>
+  </si>
+  <si>
+    <t>Soldier/Hero10_1</t>
   </si>
   <si>
     <t>关羽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>关羽(三)</t>
+  </si>
+  <si>
+    <t>Soldier/Hero11_1</t>
   </si>
   <si>
     <t>张飞</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>张飞(三)</t>
+  </si>
+  <si>
+    <t>Soldier/Hero12_1</t>
   </si>
   <si>
     <t>赵云</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>吕布(三)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>刘备(三)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>关羽(三)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>张飞(三)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>赵云(三)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soldier/Hero13_1</t>
   </si>
   <si>
     <t>项羽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>项羽(秦)</t>
+  </si>
+  <si>
+    <t>Soldier/Hero33_1</t>
   </si>
   <si>
     <t>刘邦</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘邦(秦)</t>
+  </si>
+  <si>
+    <t>Soldier/Hero43_1</t>
   </si>
   <si>
     <t>韩信</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>韩信(秦)</t>
+  </si>
+  <si>
+    <t>Soldier/Hero34_1</t>
   </si>
   <si>
     <t>樊哙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>樊哙(秦)</t>
+  </si>
+  <si>
+    <t>Soldier/Hero26_1</t>
   </si>
   <si>
     <t>项庄</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>项羽(秦)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>刘邦(秦)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>韩信(秦)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>樊哙(秦)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>项庄(秦)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Soldier/Hero13_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Soldier/Hero12_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Soldier/Hero22_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Soldier/Hero10_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Soldier/Hero11_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Soldier/Hero33_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Soldier/Hero26_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Soldier/Hero43_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Soldier/Hero38_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Soldier/Hero34_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>unitType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0无 1刀2枪3骑  11 攻城器 101英雄     （兵种属性和克制 1 克 2 ， 2 克 3， 3克1 ， 0被所有克)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -449,24 +704,310 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -724,121 +1265,116 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:J31"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
-    <col min="2" max="3" width="18.08203125" customWidth="1"/>
-    <col min="4" max="4" width="19.4140625" customWidth="1"/>
-    <col min="6" max="9" width="81.83203125" customWidth="1"/>
+    <col min="2" max="3" width="18.0833333333333" customWidth="1"/>
+    <col min="4" max="4" width="19.4166666666667" customWidth="1"/>
+    <col min="6" max="9" width="81.8333333333333" customWidth="1"/>
     <col min="10" max="10" width="57.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H1" t="s">
-        <v>19</v>
-      </c>
       <c r="I1" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I2" t="s">
-        <v>96</v>
+        <v>10</v>
       </c>
       <c r="J2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" t="s">
         <v>22</v>
       </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" t="s">
-        <v>97</v>
-      </c>
       <c r="J3" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -849,7 +1385,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -870,7 +1406,7 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -878,10 +1414,10 @@
         <v>102</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -902,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -910,10 +1446,10 @@
         <v>103</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -934,7 +1470,7 @@
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -942,10 +1478,10 @@
         <v>104</v>
       </c>
       <c r="B7" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -966,7 +1502,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -974,10 +1510,10 @@
         <v>105</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -998,7 +1534,7 @@
         <v>2</v>
       </c>
       <c r="J8" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1006,10 +1542,10 @@
         <v>106</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -1030,7 +1566,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1038,10 +1574,10 @@
         <v>107</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1062,7 +1598,7 @@
         <v>2</v>
       </c>
       <c r="J10" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1070,10 +1606,10 @@
         <v>108</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D11">
         <v>2</v>
@@ -1094,7 +1630,7 @@
         <v>11</v>
       </c>
       <c r="J11" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1102,10 +1638,10 @@
         <v>109</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="C12" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -1126,7 +1662,7 @@
         <v>3</v>
       </c>
       <c r="J12" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1134,10 +1670,10 @@
         <v>110</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -1158,7 +1694,7 @@
         <v>11</v>
       </c>
       <c r="J13" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -1166,10 +1702,10 @@
         <v>111</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="C14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -1190,7 +1726,7 @@
         <v>11</v>
       </c>
       <c r="J14" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1222,7 +1758,7 @@
         <v>1</v>
       </c>
       <c r="J15" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -1230,10 +1766,10 @@
         <v>202</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -1254,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -1262,10 +1798,10 @@
         <v>203</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C17" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -1286,7 +1822,7 @@
         <v>2</v>
       </c>
       <c r="J17" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -1294,10 +1830,10 @@
         <v>204</v>
       </c>
       <c r="B18" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C18" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -1318,7 +1854,7 @@
         <v>3</v>
       </c>
       <c r="J18" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -1326,10 +1862,10 @@
         <v>205</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D19">
         <v>2</v>
@@ -1350,7 +1886,7 @@
         <v>11</v>
       </c>
       <c r="J19" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -1358,10 +1894,10 @@
         <v>206</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="C20" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D20">
         <v>2</v>
@@ -1382,7 +1918,7 @@
         <v>11</v>
       </c>
       <c r="J20" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -1390,10 +1926,10 @@
         <v>207</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="C21" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -1414,7 +1950,7 @@
         <v>11</v>
       </c>
       <c r="J21" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -1422,10 +1958,10 @@
         <v>1001</v>
       </c>
       <c r="B22" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C22" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1446,7 +1982,7 @@
         <v>101</v>
       </c>
       <c r="J22" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -1454,10 +1990,10 @@
         <v>1002</v>
       </c>
       <c r="B23" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -1478,7 +2014,7 @@
         <v>101</v>
       </c>
       <c r="J23" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -1486,10 +2022,10 @@
         <v>1003</v>
       </c>
       <c r="B24" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="C24" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1510,7 +2046,7 @@
         <v>101</v>
       </c>
       <c r="J24" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -1518,10 +2054,10 @@
         <v>1004</v>
       </c>
       <c r="B25" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="C25" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -1542,7 +2078,7 @@
         <v>101</v>
       </c>
       <c r="J25" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -1550,10 +2086,10 @@
         <v>1005</v>
       </c>
       <c r="B26" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="C26" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1582,10 +2118,10 @@
         <v>2001</v>
       </c>
       <c r="B27" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="C27" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -1606,7 +2142,7 @@
         <v>101</v>
       </c>
       <c r="J27" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -1614,10 +2150,10 @@
         <v>2002</v>
       </c>
       <c r="B28" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="C28" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -1638,7 +2174,7 @@
         <v>101</v>
       </c>
       <c r="J28" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -1646,10 +2182,10 @@
         <v>2003</v>
       </c>
       <c r="B29" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="C29" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -1678,10 +2214,10 @@
         <v>2004</v>
       </c>
       <c r="B30" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -1702,7 +2238,7 @@
         <v>101</v>
       </c>
       <c r="J30" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -1710,10 +2246,10 @@
         <v>2005</v>
       </c>
       <c r="B31" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="C31" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -1734,11 +2270,11 @@
         <v>101</v>
       </c>
       <c r="J31" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Excels/SoliderUnit.xlsx
+++ b/Excels/SoliderUnit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11775"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11780"/>
   </bookViews>
   <sheets>
     <sheet name="SoliderCfg" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="124519"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -95,9 +95,6 @@
     <t>身体范围</t>
   </si>
   <si>
-    <t>0无 1刀2枪3骑  11 攻城器 101英雄     （兵种属性和克制 1 克 2 ， 2 克 3， 3克1 ， 0被所有克)</t>
-  </si>
-  <si>
     <t>预制体名字</t>
   </si>
   <si>
@@ -330,19 +327,17 @@
   </si>
   <si>
     <t>Soldier/Hero38_1</t>
+  </si>
+  <si>
+    <t>0无 1刀2枪3骑  11 攻城器 101英雄     （兵种属性和克制 1 克 2 ， 2 克 3， 3克1 ， 0没有克制关系)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -351,352 +346,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="9"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -704,306 +368,17 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1265,19 +640,19 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
-    <col min="2" max="3" width="18.0833333333333" customWidth="1"/>
-    <col min="4" max="4" width="19.4166666666667" customWidth="1"/>
-    <col min="6" max="9" width="81.8333333333333" customWidth="1"/>
+    <col min="2" max="3" width="18.08203125" customWidth="1"/>
+    <col min="4" max="4" width="19.4140625" customWidth="1"/>
+    <col min="6" max="9" width="81.83203125" customWidth="1"/>
     <col min="10" max="10" width="57.25" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1371,10 +746,10 @@
         <v>21</v>
       </c>
       <c r="I3" t="s">
+        <v>100</v>
+      </c>
+      <c r="J3" t="s">
         <v>22</v>
-      </c>
-      <c r="J3" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1382,31 +757,31 @@
         <v>101</v>
       </c>
       <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
         <v>24</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4" t="s">
         <v>25</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1414,10 +789,10 @@
         <v>102</v>
       </c>
       <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
         <v>27</v>
-      </c>
-      <c r="C5" t="s">
-        <v>28</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -1438,7 +813,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1446,31 +821,31 @@
         <v>103</v>
       </c>
       <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
         <v>30</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6" t="s">
         <v>31</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1478,10 +853,10 @@
         <v>104</v>
       </c>
       <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
         <v>33</v>
-      </c>
-      <c r="C7" t="s">
-        <v>34</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -1502,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1510,10 +885,10 @@
         <v>105</v>
       </c>
       <c r="B8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" t="s">
         <v>36</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1534,7 +909,7 @@
         <v>2</v>
       </c>
       <c r="J8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1542,10 +917,10 @@
         <v>106</v>
       </c>
       <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" t="s">
         <v>39</v>
-      </c>
-      <c r="C9" t="s">
-        <v>40</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -1566,7 +941,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1574,10 +949,10 @@
         <v>107</v>
       </c>
       <c r="B10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" t="s">
         <v>42</v>
-      </c>
-      <c r="C10" t="s">
-        <v>43</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1598,7 +973,7 @@
         <v>2</v>
       </c>
       <c r="J10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1606,10 +981,10 @@
         <v>108</v>
       </c>
       <c r="B11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" t="s">
         <v>45</v>
-      </c>
-      <c r="C11" t="s">
-        <v>46</v>
       </c>
       <c r="D11">
         <v>2</v>
@@ -1630,7 +1005,7 @@
         <v>11</v>
       </c>
       <c r="J11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1638,10 +1013,10 @@
         <v>109</v>
       </c>
       <c r="B12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" t="s">
         <v>48</v>
-      </c>
-      <c r="C12" t="s">
-        <v>49</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -1662,7 +1037,7 @@
         <v>3</v>
       </c>
       <c r="J12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1670,10 +1045,10 @@
         <v>110</v>
       </c>
       <c r="B13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" t="s">
         <v>51</v>
-      </c>
-      <c r="C13" t="s">
-        <v>52</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -1694,7 +1069,7 @@
         <v>11</v>
       </c>
       <c r="J13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -1702,10 +1077,10 @@
         <v>111</v>
       </c>
       <c r="B14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" t="s">
         <v>54</v>
-      </c>
-      <c r="C14" t="s">
-        <v>55</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -1726,7 +1101,7 @@
         <v>11</v>
       </c>
       <c r="J14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1734,31 +1109,31 @@
         <v>201</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15" t="s">
         <v>57</v>
-      </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15">
-        <v>1</v>
-      </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-      <c r="H15">
-        <v>1</v>
-      </c>
-      <c r="I15">
-        <v>1</v>
-      </c>
-      <c r="J15" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -1766,10 +1141,10 @@
         <v>202</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -1790,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -1798,10 +1173,10 @@
         <v>203</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -1822,7 +1197,7 @@
         <v>2</v>
       </c>
       <c r="J17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -1830,10 +1205,10 @@
         <v>204</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C18" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -1854,7 +1229,7 @@
         <v>3</v>
       </c>
       <c r="J18" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -1862,10 +1237,10 @@
         <v>205</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D19">
         <v>2</v>
@@ -1886,7 +1261,7 @@
         <v>11</v>
       </c>
       <c r="J19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -1894,10 +1269,10 @@
         <v>206</v>
       </c>
       <c r="B20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D20">
         <v>2</v>
@@ -1918,7 +1293,7 @@
         <v>11</v>
       </c>
       <c r="J20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -1926,10 +1301,10 @@
         <v>207</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -1950,7 +1325,7 @@
         <v>11</v>
       </c>
       <c r="J21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -1958,10 +1333,10 @@
         <v>1001</v>
       </c>
       <c r="B22" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" t="s">
         <v>71</v>
-      </c>
-      <c r="C22" t="s">
-        <v>72</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1982,7 +1357,7 @@
         <v>101</v>
       </c>
       <c r="J22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -1990,10 +1365,10 @@
         <v>1002</v>
       </c>
       <c r="B23" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" t="s">
         <v>74</v>
-      </c>
-      <c r="C23" t="s">
-        <v>75</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -2014,7 +1389,7 @@
         <v>101</v>
       </c>
       <c r="J23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -2022,10 +1397,10 @@
         <v>1003</v>
       </c>
       <c r="B24" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" t="s">
         <v>77</v>
-      </c>
-      <c r="C24" t="s">
-        <v>78</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -2046,7 +1421,7 @@
         <v>101</v>
       </c>
       <c r="J24" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -2054,10 +1429,10 @@
         <v>1004</v>
       </c>
       <c r="B25" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" t="s">
         <v>80</v>
-      </c>
-      <c r="C25" t="s">
-        <v>81</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -2078,7 +1453,7 @@
         <v>101</v>
       </c>
       <c r="J25" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -2086,10 +1461,10 @@
         <v>1005</v>
       </c>
       <c r="B26" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" t="s">
         <v>83</v>
-      </c>
-      <c r="C26" t="s">
-        <v>84</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -2110,7 +1485,7 @@
         <v>101</v>
       </c>
       <c r="J26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -2118,10 +1493,10 @@
         <v>2001</v>
       </c>
       <c r="B27" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" t="s">
         <v>86</v>
-      </c>
-      <c r="C27" t="s">
-        <v>87</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -2142,7 +1517,7 @@
         <v>101</v>
       </c>
       <c r="J27" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -2150,10 +1525,10 @@
         <v>2002</v>
       </c>
       <c r="B28" t="s">
+        <v>88</v>
+      </c>
+      <c r="C28" t="s">
         <v>89</v>
-      </c>
-      <c r="C28" t="s">
-        <v>90</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -2174,7 +1549,7 @@
         <v>101</v>
       </c>
       <c r="J28" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -2182,10 +1557,10 @@
         <v>2003</v>
       </c>
       <c r="B29" t="s">
+        <v>91</v>
+      </c>
+      <c r="C29" t="s">
         <v>92</v>
-      </c>
-      <c r="C29" t="s">
-        <v>93</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -2206,7 +1581,7 @@
         <v>101</v>
       </c>
       <c r="J29" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -2214,10 +1589,10 @@
         <v>2004</v>
       </c>
       <c r="B30" t="s">
+        <v>94</v>
+      </c>
+      <c r="C30" t="s">
         <v>95</v>
-      </c>
-      <c r="C30" t="s">
-        <v>96</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -2238,7 +1613,7 @@
         <v>101</v>
       </c>
       <c r="J30" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -2246,10 +1621,10 @@
         <v>2005</v>
       </c>
       <c r="B31" t="s">
+        <v>97</v>
+      </c>
+      <c r="C31" t="s">
         <v>98</v>
-      </c>
-      <c r="C31" t="s">
-        <v>99</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -2270,11 +1645,11 @@
         <v>101</v>
       </c>
       <c r="J31" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Excels/SoliderUnit.xlsx
+++ b/Excels/SoliderUnit.xlsx
@@ -1,15 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\unityProjects\GameWorldIsMine\WorldIsMine\Excels\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11780"/>
+    <workbookView windowWidth="28800" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="SoliderCfg" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -95,6 +100,9 @@
     <t>身体范围</t>
   </si>
   <si>
+    <t>0无 1刀2枪3骑  11 攻城器 101英雄     （兵种属性和克制 1 克 2 ， 2 克 3， 3克1 ， 0没有克制关系)</t>
+  </si>
+  <si>
     <t>预制体名字</t>
   </si>
   <si>
@@ -327,17 +335,19 @@
   </si>
   <si>
     <t>Soldier/Hero38_1</t>
-  </si>
-  <si>
-    <t>0无 1刀2枪3骑  11 攻城器 101英雄     （兵种属性和克制 1 克 2 ， 2 克 3， 3克1 ， 0没有克制关系)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -346,21 +356,345 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -368,17 +702,306 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -640,19 +1263,19 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:J31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
-    <col min="2" max="3" width="18.08203125" customWidth="1"/>
-    <col min="4" max="4" width="19.4140625" customWidth="1"/>
-    <col min="6" max="9" width="81.83203125" customWidth="1"/>
+    <col min="2" max="3" width="18.0833333333333" customWidth="1"/>
+    <col min="4" max="4" width="19.4166666666667" customWidth="1"/>
+    <col min="6" max="9" width="81.8333333333333" customWidth="1"/>
     <col min="10" max="10" width="57.25" customWidth="1"/>
   </cols>
   <sheetData>
@@ -746,10 +1369,10 @@
         <v>21</v>
       </c>
       <c r="I3" t="s">
-        <v>100</v>
+        <v>22</v>
       </c>
       <c r="J3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -757,10 +1380,10 @@
         <v>101</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -772,16 +1395,16 @@
         <v>1</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I4">
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -789,10 +1412,10 @@
         <v>102</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -804,7 +1427,7 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -813,7 +1436,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -821,10 +1444,10 @@
         <v>103</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -845,7 +1468,7 @@
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -853,10 +1476,10 @@
         <v>104</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -877,7 +1500,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -885,10 +1508,10 @@
         <v>105</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -909,7 +1532,7 @@
         <v>2</v>
       </c>
       <c r="J8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -917,10 +1540,10 @@
         <v>106</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -941,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -949,10 +1572,10 @@
         <v>107</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -973,7 +1596,7 @@
         <v>2</v>
       </c>
       <c r="J10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -981,10 +1604,10 @@
         <v>108</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D11">
         <v>2</v>
@@ -1005,7 +1628,7 @@
         <v>11</v>
       </c>
       <c r="J11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1013,13 +1636,13 @@
         <v>109</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -1028,7 +1651,7 @@
         <v>1</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -1037,7 +1660,7 @@
         <v>3</v>
       </c>
       <c r="J12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1045,10 +1668,10 @@
         <v>110</v>
       </c>
       <c r="B13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -1069,7 +1692,7 @@
         <v>11</v>
       </c>
       <c r="J13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -1077,10 +1700,10 @@
         <v>111</v>
       </c>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -1101,7 +1724,7 @@
         <v>11</v>
       </c>
       <c r="J14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1109,10 +1732,10 @@
         <v>201</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -1124,16 +1747,16 @@
         <v>1</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H15">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I15">
         <v>1</v>
       </c>
       <c r="J15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -1141,10 +1764,10 @@
         <v>202</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -1156,7 +1779,7 @@
         <v>1</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -1165,7 +1788,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -1173,10 +1796,10 @@
         <v>203</v>
       </c>
       <c r="B17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -1197,7 +1820,7 @@
         <v>2</v>
       </c>
       <c r="J17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -1205,13 +1828,13 @@
         <v>204</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C18" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -1220,7 +1843,7 @@
         <v>1</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -1229,7 +1852,7 @@
         <v>3</v>
       </c>
       <c r="J18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -1237,10 +1860,10 @@
         <v>205</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D19">
         <v>2</v>
@@ -1261,7 +1884,7 @@
         <v>11</v>
       </c>
       <c r="J19" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -1269,10 +1892,10 @@
         <v>206</v>
       </c>
       <c r="B20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C20" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D20">
         <v>2</v>
@@ -1293,7 +1916,7 @@
         <v>11</v>
       </c>
       <c r="J20" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -1301,10 +1924,10 @@
         <v>207</v>
       </c>
       <c r="B21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C21" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -1325,7 +1948,7 @@
         <v>11</v>
       </c>
       <c r="J21" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -1333,10 +1956,10 @@
         <v>1001</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1357,7 +1980,7 @@
         <v>101</v>
       </c>
       <c r="J22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -1365,10 +1988,10 @@
         <v>1002</v>
       </c>
       <c r="B23" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -1389,7 +2012,7 @@
         <v>101</v>
       </c>
       <c r="J23" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -1397,10 +2020,10 @@
         <v>1003</v>
       </c>
       <c r="B24" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1421,7 +2044,7 @@
         <v>101</v>
       </c>
       <c r="J24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -1429,10 +2052,10 @@
         <v>1004</v>
       </c>
       <c r="B25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C25" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -1453,7 +2076,7 @@
         <v>101</v>
       </c>
       <c r="J25" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -1461,10 +2084,10 @@
         <v>1005</v>
       </c>
       <c r="B26" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C26" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1485,7 +2108,7 @@
         <v>101</v>
       </c>
       <c r="J26" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -1493,10 +2116,10 @@
         <v>2001</v>
       </c>
       <c r="B27" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C27" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -1517,7 +2140,7 @@
         <v>101</v>
       </c>
       <c r="J27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -1525,10 +2148,10 @@
         <v>2002</v>
       </c>
       <c r="B28" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C28" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -1549,7 +2172,7 @@
         <v>101</v>
       </c>
       <c r="J28" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -1557,10 +2180,10 @@
         <v>2003</v>
       </c>
       <c r="B29" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C29" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -1581,7 +2204,7 @@
         <v>101</v>
       </c>
       <c r="J29" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -1589,10 +2212,10 @@
         <v>2004</v>
       </c>
       <c r="B30" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -1613,7 +2236,7 @@
         <v>101</v>
       </c>
       <c r="J30" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -1621,10 +2244,10 @@
         <v>2005</v>
       </c>
       <c r="B31" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C31" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -1645,11 +2268,11 @@
         <v>101</v>
       </c>
       <c r="J31" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Excels/SoliderUnit.xlsx
+++ b/Excels/SoliderUnit.xlsx
@@ -1,20 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\unityProjects\GameWorldIsMine\WorldIsMine\Excels\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11775"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11780"/>
   </bookViews>
   <sheets>
     <sheet name="SoliderCfg" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="124519"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="109">
   <si>
     <t>id</t>
   </si>
@@ -100,9 +95,6 @@
     <t>身体范围</t>
   </si>
   <si>
-    <t>0无 1刀2枪3骑  11 攻城器 101英雄     （兵种属性和克制 1 克 2 ， 2 克 3， 3克1 ， 0没有克制关系)</t>
-  </si>
-  <si>
     <t>预制体名字</t>
   </si>
   <si>
@@ -335,19 +327,49 @@
   </si>
   <si>
     <t>Soldier/Hero38_1</t>
+  </si>
+  <si>
+    <t>0无 1刀2枪3骑  11 攻城器 101英雄 1001建筑    （兵种属性和克制 1 克 2 ， 2 克 3， 3克1 ， 0没有克制关系， 11克1001，101英雄全克制)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>restrainValue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>克制比例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>城门</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>城门(三)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>City/Door</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>城门(秦)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>City/Door_qin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -356,345 +378,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -702,306 +400,17 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1263,23 +672,24 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:J31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K33"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
-    <col min="2" max="3" width="18.0833333333333" customWidth="1"/>
-    <col min="4" max="4" width="19.4166666666667" customWidth="1"/>
-    <col min="6" max="9" width="81.8333333333333" customWidth="1"/>
-    <col min="10" max="10" width="57.25" customWidth="1"/>
+    <col min="2" max="3" width="18.08203125" customWidth="1"/>
+    <col min="4" max="4" width="19.4140625" customWidth="1"/>
+    <col min="6" max="8" width="81.83203125" customWidth="1"/>
+    <col min="9" max="10" width="135.75" customWidth="1"/>
+    <col min="11" max="11" width="57.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1308,10 +718,13 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
+        <v>101</v>
+      </c>
+      <c r="K1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1340,10 +753,13 @@
         <v>10</v>
       </c>
       <c r="J2" t="s">
+        <v>102</v>
+      </c>
+      <c r="K2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1369,21 +785,24 @@
         <v>21</v>
       </c>
       <c r="I3" t="s">
+        <v>100</v>
+      </c>
+      <c r="J3" t="s">
+        <v>103</v>
+      </c>
+      <c r="K3" t="s">
         <v>22</v>
       </c>
-      <c r="J3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4">
         <v>101</v>
       </c>
       <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
         <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1403,19 +822,22 @@
       <c r="I4">
         <v>1</v>
       </c>
-      <c r="J4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="J4">
+        <v>1.5</v>
+      </c>
+      <c r="K4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>102</v>
       </c>
       <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
         <v>27</v>
-      </c>
-      <c r="C5" t="s">
-        <v>28</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -1435,51 +857,57 @@
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="J5">
+        <v>1.5</v>
+      </c>
+      <c r="K5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6">
         <v>103</v>
       </c>
       <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
         <v>30</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1.5</v>
+      </c>
+      <c r="K6" t="s">
         <v>31</v>
       </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7">
         <v>104</v>
       </c>
       <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
         <v>33</v>
-      </c>
-      <c r="C7" t="s">
-        <v>34</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -1499,19 +927,22 @@
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+      <c r="J7">
+        <v>1.5</v>
+      </c>
+      <c r="K7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8">
         <v>105</v>
       </c>
       <c r="B8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" t="s">
         <v>36</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1531,19 +962,22 @@
       <c r="I8">
         <v>2</v>
       </c>
-      <c r="J8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+      <c r="J8">
+        <v>1.5</v>
+      </c>
+      <c r="K8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9">
         <v>106</v>
       </c>
       <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" t="s">
         <v>39</v>
-      </c>
-      <c r="C9" t="s">
-        <v>40</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -1563,19 +997,22 @@
       <c r="I9">
         <v>0</v>
       </c>
-      <c r="J9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+      <c r="J9">
+        <v>1.5</v>
+      </c>
+      <c r="K9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10">
         <v>107</v>
       </c>
       <c r="B10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" t="s">
         <v>42</v>
-      </c>
-      <c r="C10" t="s">
-        <v>43</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1595,19 +1032,22 @@
       <c r="I10">
         <v>2</v>
       </c>
-      <c r="J10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+      <c r="J10">
+        <v>1.5</v>
+      </c>
+      <c r="K10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11">
         <v>108</v>
       </c>
       <c r="B11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" t="s">
         <v>45</v>
-      </c>
-      <c r="C11" t="s">
-        <v>46</v>
       </c>
       <c r="D11">
         <v>2</v>
@@ -1627,19 +1067,22 @@
       <c r="I11">
         <v>11</v>
       </c>
-      <c r="J11" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+      <c r="J11">
+        <v>1.5</v>
+      </c>
+      <c r="K11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12">
         <v>109</v>
       </c>
       <c r="B12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" t="s">
         <v>48</v>
-      </c>
-      <c r="C12" t="s">
-        <v>49</v>
       </c>
       <c r="D12">
         <v>3</v>
@@ -1659,19 +1102,22 @@
       <c r="I12">
         <v>3</v>
       </c>
-      <c r="J12" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+      <c r="J12">
+        <v>1.5</v>
+      </c>
+      <c r="K12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13">
         <v>110</v>
       </c>
       <c r="B13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" t="s">
         <v>51</v>
-      </c>
-      <c r="C13" t="s">
-        <v>52</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -1691,19 +1137,22 @@
       <c r="I13">
         <v>11</v>
       </c>
-      <c r="J13" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+      <c r="J13">
+        <v>1.5</v>
+      </c>
+      <c r="K13" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14">
         <v>111</v>
       </c>
       <c r="B14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" t="s">
         <v>54</v>
-      </c>
-      <c r="C14" t="s">
-        <v>55</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -1723,19 +1172,22 @@
       <c r="I14">
         <v>11</v>
       </c>
-      <c r="J14" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+      <c r="J14">
+        <v>1.5</v>
+      </c>
+      <c r="K14" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15">
         <v>201</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -1755,19 +1207,22 @@
       <c r="I15">
         <v>1</v>
       </c>
-      <c r="J15" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+      <c r="J15">
+        <v>1.5</v>
+      </c>
+      <c r="K15" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16">
         <v>202</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -1787,19 +1242,22 @@
       <c r="I16">
         <v>0</v>
       </c>
-      <c r="J16" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
+      <c r="J16">
+        <v>1.5</v>
+      </c>
+      <c r="K16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17">
         <v>203</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -1819,19 +1277,22 @@
       <c r="I17">
         <v>2</v>
       </c>
-      <c r="J17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+      <c r="J17">
+        <v>1.5</v>
+      </c>
+      <c r="K17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18">
         <v>204</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C18" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D18">
         <v>3</v>
@@ -1851,19 +1312,22 @@
       <c r="I18">
         <v>3</v>
       </c>
-      <c r="J18" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+      <c r="J18">
+        <v>1.5</v>
+      </c>
+      <c r="K18" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19">
         <v>205</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D19">
         <v>2</v>
@@ -1883,19 +1347,22 @@
       <c r="I19">
         <v>11</v>
       </c>
-      <c r="J19" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+      <c r="J19">
+        <v>1.5</v>
+      </c>
+      <c r="K19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20">
         <v>206</v>
       </c>
       <c r="B20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D20">
         <v>2</v>
@@ -1915,19 +1382,22 @@
       <c r="I20">
         <v>11</v>
       </c>
-      <c r="J20" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+      <c r="J20">
+        <v>1.5</v>
+      </c>
+      <c r="K20" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21">
         <v>207</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -1947,19 +1417,22 @@
       <c r="I21">
         <v>11</v>
       </c>
-      <c r="J21" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
+      <c r="J21">
+        <v>1.5</v>
+      </c>
+      <c r="K21" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22">
         <v>1001</v>
       </c>
       <c r="B22" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" t="s">
         <v>71</v>
-      </c>
-      <c r="C22" t="s">
-        <v>72</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1979,19 +1452,22 @@
       <c r="I22">
         <v>101</v>
       </c>
-      <c r="J22" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
+      <c r="J22">
+        <v>1.5</v>
+      </c>
+      <c r="K22" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23">
         <v>1002</v>
       </c>
       <c r="B23" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" t="s">
         <v>74</v>
-      </c>
-      <c r="C23" t="s">
-        <v>75</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -2011,19 +1487,22 @@
       <c r="I23">
         <v>101</v>
       </c>
-      <c r="J23" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
+      <c r="J23">
+        <v>1.5</v>
+      </c>
+      <c r="K23" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24">
         <v>1003</v>
       </c>
       <c r="B24" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" t="s">
         <v>77</v>
-      </c>
-      <c r="C24" t="s">
-        <v>78</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -2043,19 +1522,22 @@
       <c r="I24">
         <v>101</v>
       </c>
-      <c r="J24" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
+      <c r="J24">
+        <v>1.5</v>
+      </c>
+      <c r="K24" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25">
         <v>1004</v>
       </c>
       <c r="B25" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" t="s">
         <v>80</v>
-      </c>
-      <c r="C25" t="s">
-        <v>81</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -2075,19 +1557,22 @@
       <c r="I25">
         <v>101</v>
       </c>
-      <c r="J25" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
+      <c r="J25">
+        <v>1.5</v>
+      </c>
+      <c r="K25" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26">
         <v>1005</v>
       </c>
       <c r="B26" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" t="s">
         <v>83</v>
-      </c>
-      <c r="C26" t="s">
-        <v>84</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -2107,19 +1592,22 @@
       <c r="I26">
         <v>101</v>
       </c>
-      <c r="J26" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
+      <c r="J26">
+        <v>1.5</v>
+      </c>
+      <c r="K26" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27">
         <v>2001</v>
       </c>
       <c r="B27" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" t="s">
         <v>86</v>
-      </c>
-      <c r="C27" t="s">
-        <v>87</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -2139,19 +1627,22 @@
       <c r="I27">
         <v>101</v>
       </c>
-      <c r="J27" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
+      <c r="J27">
+        <v>1.5</v>
+      </c>
+      <c r="K27" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
       <c r="A28">
         <v>2002</v>
       </c>
       <c r="B28" t="s">
+        <v>88</v>
+      </c>
+      <c r="C28" t="s">
         <v>89</v>
-      </c>
-      <c r="C28" t="s">
-        <v>90</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -2171,19 +1662,22 @@
       <c r="I28">
         <v>101</v>
       </c>
-      <c r="J28" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
+      <c r="J28">
+        <v>1.5</v>
+      </c>
+      <c r="K28" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
       <c r="A29">
         <v>2003</v>
       </c>
       <c r="B29" t="s">
+        <v>91</v>
+      </c>
+      <c r="C29" t="s">
         <v>92</v>
-      </c>
-      <c r="C29" t="s">
-        <v>93</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -2203,19 +1697,22 @@
       <c r="I29">
         <v>101</v>
       </c>
-      <c r="J29" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
+      <c r="J29">
+        <v>1.5</v>
+      </c>
+      <c r="K29" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
       <c r="A30">
         <v>2004</v>
       </c>
       <c r="B30" t="s">
+        <v>94</v>
+      </c>
+      <c r="C30" t="s">
         <v>95</v>
-      </c>
-      <c r="C30" t="s">
-        <v>96</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -2235,19 +1732,22 @@
       <c r="I30">
         <v>101</v>
       </c>
-      <c r="J30" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
+      <c r="J30">
+        <v>1.5</v>
+      </c>
+      <c r="K30" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
       <c r="A31">
         <v>2005</v>
       </c>
       <c r="B31" t="s">
+        <v>97</v>
+      </c>
+      <c r="C31" t="s">
         <v>98</v>
-      </c>
-      <c r="C31" t="s">
-        <v>99</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -2267,12 +1767,85 @@
       <c r="I31">
         <v>101</v>
       </c>
-      <c r="J31" t="s">
-        <v>100</v>
+      <c r="J31">
+        <v>1.5</v>
+      </c>
+      <c r="K31" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32">
+        <v>10001</v>
+      </c>
+      <c r="B32" t="s">
+        <v>104</v>
+      </c>
+      <c r="C32" t="s">
+        <v>105</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>1001</v>
+      </c>
+      <c r="J32">
+        <v>1</v>
+      </c>
+      <c r="K32" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33">
+        <v>20001</v>
+      </c>
+      <c r="B33" t="s">
+        <v>104</v>
+      </c>
+      <c r="C33" t="s">
+        <v>107</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>1</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>1001</v>
+      </c>
+      <c r="J33">
+        <v>1</v>
+      </c>
+      <c r="K33" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Excels/SoliderUnit.xlsx
+++ b/Excels/SoliderUnit.xlsx
@@ -808,7 +808,7 @@
         <v>1</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -843,7 +843,7 @@
         <v>2</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -878,7 +878,7 @@
         <v>1</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -913,7 +913,7 @@
         <v>2</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -948,7 +948,7 @@
         <v>1</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -983,7 +983,7 @@
         <v>2</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -1018,7 +1018,7 @@
         <v>1</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -1053,7 +1053,7 @@
         <v>2</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -1088,7 +1088,7 @@
         <v>3</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -1123,7 +1123,7 @@
         <v>2</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -1158,7 +1158,7 @@
         <v>1</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -1193,7 +1193,7 @@
         <v>1</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -1228,7 +1228,7 @@
         <v>2</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -1263,7 +1263,7 @@
         <v>1</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -1298,7 +1298,7 @@
         <v>3</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -1333,7 +1333,7 @@
         <v>2</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -1368,7 +1368,7 @@
         <v>2</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -1473,7 +1473,7 @@
         <v>0</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -1508,7 +1508,7 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -1578,7 +1578,7 @@
         <v>0</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -1613,7 +1613,7 @@
         <v>0</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F27">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F28">
         <v>1</v>
@@ -1683,7 +1683,7 @@
         <v>0</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F29">
         <v>1</v>
@@ -1718,7 +1718,7 @@
         <v>0</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -1753,7 +1753,7 @@
         <v>0</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -1788,7 +1788,7 @@
         <v>0</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -1823,7 +1823,7 @@
         <v>0</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F33">
         <v>1</v>

--- a/Excels/SoliderUnit.xlsx
+++ b/Excels/SoliderUnit.xlsx
@@ -1,15 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\unityProjects\GameWorldIsMine\WorldIsMine\Excels\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11780"/>
+    <workbookView windowWidth="28800" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="SoliderCfg" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="108">
   <si>
     <t>id</t>
   </si>
@@ -56,6 +61,9 @@
     <t>unitType</t>
   </si>
   <si>
+    <t>restrainValue</t>
+  </si>
+  <si>
     <t>prefab</t>
   </si>
   <si>
@@ -95,6 +103,12 @@
     <t>身体范围</t>
   </si>
   <si>
+    <t>0无 1刀2枪3骑  11 攻城器 101英雄 1001建筑    （兵种属性和克制 1 克 2 ， 2 克 3， 3克1 ， 0没有克制关系， 11克1001，101英雄全克制)</t>
+  </si>
+  <si>
+    <t>克制比例</t>
+  </si>
+  <si>
     <t>预制体名字</t>
   </si>
   <si>
@@ -329,47 +343,32 @@
     <t>Soldier/Hero38_1</t>
   </si>
   <si>
-    <t>0无 1刀2枪3骑  11 攻城器 101英雄 1001建筑    （兵种属性和克制 1 克 2 ， 2 克 3， 3克1 ， 0没有克制关系， 11克1001，101英雄全克制)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>restrainValue</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>float</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>克制比例</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>城门</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>城门(三)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>City/Door</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>城门(秦)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>City/Door_qin</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -378,21 +377,345 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -400,17 +723,306 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -672,19 +1284,19 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:K33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
-    <col min="2" max="3" width="18.08203125" customWidth="1"/>
-    <col min="4" max="4" width="19.4140625" customWidth="1"/>
-    <col min="6" max="8" width="81.83203125" customWidth="1"/>
+    <col min="2" max="3" width="18.0833333333333" customWidth="1"/>
+    <col min="4" max="4" width="19.4166666666667" customWidth="1"/>
+    <col min="6" max="8" width="81.8333333333333" customWidth="1"/>
     <col min="9" max="10" width="135.75" customWidth="1"/>
     <col min="11" max="11" width="57.25" customWidth="1"/>
   </cols>
@@ -718,80 +1330,80 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>101</v>
+        <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" t="s">
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" t="s">
         <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I3" t="s">
-        <v>100</v>
+        <v>23</v>
       </c>
       <c r="J3" t="s">
-        <v>103</v>
+        <v>24</v>
       </c>
       <c r="K3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -799,16 +1411,16 @@
         <v>101</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -826,7 +1438,7 @@
         <v>1.5</v>
       </c>
       <c r="K4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -834,16 +1446,16 @@
         <v>102</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -861,7 +1473,7 @@
         <v>1.5</v>
       </c>
       <c r="K5" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -869,16 +1481,16 @@
         <v>103</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -896,7 +1508,7 @@
         <v>1.5</v>
       </c>
       <c r="K6" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -904,16 +1516,16 @@
         <v>104</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D7">
         <v>2</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -931,7 +1543,7 @@
         <v>1.5</v>
       </c>
       <c r="K7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -939,16 +1551,16 @@
         <v>105</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -966,7 +1578,7 @@
         <v>1.5</v>
       </c>
       <c r="K8" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -974,16 +1586,16 @@
         <v>106</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D9">
         <v>2</v>
       </c>
       <c r="E9">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -1001,7 +1613,7 @@
         <v>1.5</v>
       </c>
       <c r="K9" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1009,16 +1621,16 @@
         <v>107</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -1036,7 +1648,7 @@
         <v>1.5</v>
       </c>
       <c r="K10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1044,16 +1656,16 @@
         <v>108</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D11">
         <v>2</v>
       </c>
       <c r="E11">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -1071,7 +1683,7 @@
         <v>1.5</v>
       </c>
       <c r="K11" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1079,16 +1691,16 @@
         <v>109</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D12">
         <v>3</v>
       </c>
       <c r="E12">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -1106,7 +1718,7 @@
         <v>1.5</v>
       </c>
       <c r="K12" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1114,16 +1726,16 @@
         <v>110</v>
       </c>
       <c r="B13" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D13">
         <v>2</v>
       </c>
       <c r="E13">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -1141,7 +1753,7 @@
         <v>1.5</v>
       </c>
       <c r="K13" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1149,16 +1761,16 @@
         <v>111</v>
       </c>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -1176,7 +1788,7 @@
         <v>1.5</v>
       </c>
       <c r="K14" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1184,16 +1796,16 @@
         <v>201</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="E15">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -1211,7 +1823,7 @@
         <v>1.5</v>
       </c>
       <c r="K15" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1219,16 +1831,16 @@
         <v>202</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D16">
         <v>2</v>
       </c>
       <c r="E16">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -1246,7 +1858,7 @@
         <v>1.5</v>
       </c>
       <c r="K16" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1254,16 +1866,16 @@
         <v>203</v>
       </c>
       <c r="B17" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C17" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
       <c r="E17">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -1281,7 +1893,7 @@
         <v>1.5</v>
       </c>
       <c r="K17" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1289,16 +1901,16 @@
         <v>204</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D18">
         <v>3</v>
       </c>
       <c r="E18">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -1316,7 +1928,7 @@
         <v>1.5</v>
       </c>
       <c r="K18" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1324,16 +1936,16 @@
         <v>205</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C19" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D19">
         <v>2</v>
       </c>
       <c r="E19">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -1351,7 +1963,7 @@
         <v>1.5</v>
       </c>
       <c r="K19" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1359,16 +1971,16 @@
         <v>206</v>
       </c>
       <c r="B20" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C20" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D20">
         <v>2</v>
       </c>
       <c r="E20">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -1386,7 +1998,7 @@
         <v>1.5</v>
       </c>
       <c r="K20" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1394,16 +2006,16 @@
         <v>207</v>
       </c>
       <c r="B21" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C21" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D21">
         <v>1</v>
       </c>
       <c r="E21">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -1421,7 +2033,7 @@
         <v>1.5</v>
       </c>
       <c r="K21" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1429,16 +2041,16 @@
         <v>1001</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C22" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -1456,7 +2068,7 @@
         <v>1.5</v>
       </c>
       <c r="K22" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1464,16 +2076,16 @@
         <v>1002</v>
       </c>
       <c r="B23" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C23" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
       <c r="E23">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -1491,7 +2103,7 @@
         <v>1.5</v>
       </c>
       <c r="K23" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1499,16 +2111,16 @@
         <v>1003</v>
       </c>
       <c r="B24" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C24" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
       <c r="E24">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -1526,7 +2138,7 @@
         <v>1.5</v>
       </c>
       <c r="K24" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1534,16 +2146,16 @@
         <v>1004</v>
       </c>
       <c r="B25" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -1561,7 +2173,7 @@
         <v>1.5</v>
       </c>
       <c r="K25" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1569,16 +2181,16 @@
         <v>1005</v>
       </c>
       <c r="B26" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D26">
         <v>0</v>
       </c>
       <c r="E26">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -1596,7 +2208,7 @@
         <v>1.5</v>
       </c>
       <c r="K26" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1604,16 +2216,16 @@
         <v>2001</v>
       </c>
       <c r="B27" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F27">
         <v>1</v>
@@ -1631,7 +2243,7 @@
         <v>1.5</v>
       </c>
       <c r="K27" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1639,16 +2251,16 @@
         <v>2002</v>
       </c>
       <c r="B28" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C28" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D28">
         <v>0</v>
       </c>
       <c r="E28">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F28">
         <v>1</v>
@@ -1666,7 +2278,7 @@
         <v>1.5</v>
       </c>
       <c r="K28" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1674,16 +2286,16 @@
         <v>2003</v>
       </c>
       <c r="B29" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
       <c r="E29">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F29">
         <v>1</v>
@@ -1701,7 +2313,7 @@
         <v>1.5</v>
       </c>
       <c r="K29" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1709,16 +2321,16 @@
         <v>2004</v>
       </c>
       <c r="B30" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C30" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D30">
         <v>0</v>
       </c>
       <c r="E30">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -1736,7 +2348,7 @@
         <v>1.5</v>
       </c>
       <c r="K30" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1744,16 +2356,16 @@
         <v>2005</v>
       </c>
       <c r="B31" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C31" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D31">
         <v>0</v>
       </c>
       <c r="E31">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -1771,7 +2383,7 @@
         <v>1.5</v>
       </c>
       <c r="K31" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1779,16 +2391,16 @@
         <v>10001</v>
       </c>
       <c r="B32" t="s">
+        <v>103</v>
+      </c>
+      <c r="C32" t="s">
         <v>104</v>
-      </c>
-      <c r="C32" t="s">
-        <v>105</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -1806,7 +2418,7 @@
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1814,16 +2426,16 @@
         <v>20001</v>
       </c>
       <c r="B33" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C33" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
       <c r="E33">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F33">
         <v>1</v>
@@ -1841,11 +2453,11 @@
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Excels/SoliderUnit.xlsx
+++ b/Excels/SoliderUnit.xlsx
@@ -1,15 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\unityProjects\GameWorldIsMine\WorldIsMine\Excels\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11775"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11780"/>
   </bookViews>
   <sheets>
     <sheet name="SoliderCfg" sheetId="1" r:id="rId1"/>
@@ -361,14 +356,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -377,345 +366,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -723,306 +388,17 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1284,19 +660,19 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
-    <col min="2" max="3" width="18.0833333333333" customWidth="1"/>
-    <col min="4" max="4" width="19.4166666666667" customWidth="1"/>
-    <col min="6" max="8" width="81.8333333333333" customWidth="1"/>
+    <col min="2" max="3" width="18.08203125" customWidth="1"/>
+    <col min="4" max="4" width="19.4140625" customWidth="1"/>
+    <col min="6" max="8" width="81.83203125" customWidth="1"/>
     <col min="9" max="10" width="135.75" customWidth="1"/>
     <col min="11" max="11" width="57.25" customWidth="1"/>
   </cols>
@@ -2047,7 +1423,7 @@
         <v>74</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E22">
         <v>5</v>
@@ -2082,7 +1458,7 @@
         <v>77</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E23">
         <v>5</v>
@@ -2117,7 +1493,7 @@
         <v>80</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E24">
         <v>5</v>
@@ -2152,7 +1528,7 @@
         <v>83</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E25">
         <v>5</v>
@@ -2187,7 +1563,7 @@
         <v>86</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E26">
         <v>5</v>
@@ -2222,7 +1598,7 @@
         <v>89</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E27">
         <v>5</v>
@@ -2257,7 +1633,7 @@
         <v>92</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E28">
         <v>5</v>
@@ -2292,7 +1668,7 @@
         <v>95</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E29">
         <v>5</v>
@@ -2327,7 +1703,7 @@
         <v>98</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E30">
         <v>5</v>
@@ -2362,7 +1738,7 @@
         <v>101</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E31">
         <v>5</v>
@@ -2457,7 +1833,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>